--- a/实验数据.xlsx
+++ b/实验数据.xlsx
@@ -1,32 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24703\AppData\Local\Temp\opencode\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjectVision\DINOv3_0804\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEEA1B3-C71F-4E5E-995E-2501CE4D7EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9578F5B5-8A43-4F41-BFE4-4A9D832E31C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="25580" windowHeight="15260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="20" windowWidth="25580" windowHeight="15260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="A组-PCA投影" sheetId="1" r:id="rId1"/>
     <sheet name="K组-软标签蒸馏" sheetId="3" r:id="rId2"/>
+    <sheet name="R组-关系蒸馏" sheetId="4" r:id="rId3"/>
+    <sheet name="D组-MSE改进" sheetId="5" r:id="rId4"/>
+    <sheet name="H组-激活函数" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="147">
   <si>
     <t>方案</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -366,6 +380,235 @@
   </si>
   <si>
     <t>dev small-object mIoU</t>
+  </si>
+  <si>
+    <t>K4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A0 初始化 + CE+logits KD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>相对 A0-FT 只增加 K2 logits KD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复用/知识</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K1 复现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CE+ A_best feature KD，无关系项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排除代码分支差异</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>图像关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R0+masked GAP 后的 batch B×B cosine matrix MSE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录关系梯度和 batch 大小</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>空间关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R0+池化至 8×16 后的 128×128 token 关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重点报告边界/小目标和显存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>lambda_rel =0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两种关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>relation-only</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lambda_r1=0.03 r2=0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R0+R1+R2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关系梯度为 feature 梯度的 5%–20%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CE+关系项，移除逐点 feature MSE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅诊断欠约束，不作主候选</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>feature+relation+logits</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在 R2 基础上加入 K 组已锁定的 pixel-logit KD；保留 lambda_feat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比较 R5-R2 的 logits 增量和 R5-K3 的空间关系增量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无新增分布项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分布实验锚点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>CORAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K1+共同瓶颈均值/协方差对齐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SWD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录带宽或投影数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aborted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lambda=0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K1 + SWD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复用/关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>激活</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V2 ReLU6 anchor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R5-compatible 协议；stem、inverted residual、final 1×1 和 R-ASPP 均保持原始 ReLU6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V2 Hardswish 全 in-block</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只替换 backbone.1..17 inverted residual 内所有 eligible conv.0.2/conv.1.2；stem/final/R-ASPP/linear bottleneck 不变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> V2 Hardswish 后段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只替换 backbone.14..17 内 expansion+depthwise 激活；固定 OS=16 后段主假设</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V2 Hardswish 后段 depthwise-only</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只替换 backbone.14..17 的 conv.1.2 depthwise 激活；expansion 保持 ReLU6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -411,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -425,6 +668,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -708,7 +952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -757,22 +1001,22 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="2">
         <v>42</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>15</v>
       </c>
       <c r="G2" s="3">
@@ -792,14 +1036,14 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="2">
         <v>3407</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
       <c r="G3" s="3">
         <v>0.68241200000000002</v>
       </c>
@@ -817,14 +1061,14 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="2">
         <v>260805</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
       <c r="G4" s="3">
         <v>0.68065900000000001</v>
       </c>
@@ -842,22 +1086,22 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="2">
         <v>42</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G5" s="3">
@@ -877,14 +1121,14 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="2">
         <v>3407</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
       <c r="G6" s="3">
         <v>0.77834599999999998</v>
       </c>
@@ -902,14 +1146,14 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="2">
         <v>260805</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
       <c r="G7" s="3">
         <v>0.77542</v>
       </c>
@@ -927,22 +1171,22 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="2">
         <v>42</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>21</v>
       </c>
       <c r="G8" s="3">
@@ -962,14 +1206,14 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="2">
         <v>3407</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
       <c r="G9" s="3">
         <v>0.49485600000000002</v>
       </c>
@@ -987,14 +1231,14 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="2">
         <v>260805</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
       <c r="G10" s="3">
         <v>0.501224</v>
       </c>
@@ -1047,19 +1291,19 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="2">
         <v>42</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>27</v>
       </c>
       <c r="G12" s="3">
@@ -1082,13 +1326,13 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
       <c r="C13" s="2">
         <v>3407</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
       <c r="G13" s="3">
         <v>0.50283100000000003</v>
       </c>
@@ -1106,13 +1350,13 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="2">
         <v>260805</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
       <c r="G14" s="3">
         <v>0.49548300000000001</v>
       </c>
@@ -1130,19 +1374,19 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="2">
         <v>42</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G15" s="3">
@@ -1162,13 +1406,13 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
       <c r="C16" s="2">
         <v>3407</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
       <c r="G16" s="3">
         <v>0.38905099999999998</v>
       </c>
@@ -1185,14 +1429,14 @@
         <v>0.23532623008111131</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
       <c r="C17" s="2">
         <v>260805</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
       <c r="G17" s="3">
         <v>0.400341</v>
       </c>
@@ -1209,7 +1453,7 @@
         <v>0.24791827215129053</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
@@ -1244,7 +1488,7 @@
         <v>0.24211462786074844</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>29</v>
       </c>
@@ -1279,7 +1523,7 @@
         <v>0.10797791334855912</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -1314,7 +1558,7 @@
         <v>0.15682501934085691</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -1349,23 +1593,23 @@
         <v>0.21850052917131829</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C22" s="2">
         <v>42</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G22" s="3">
@@ -1384,15 +1628,15 @@
         <v>0.24684836070491892</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
       <c r="C23" s="2">
         <v>3407</v>
       </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
       <c r="G23" s="3">
         <v>0.39770699999999998</v>
       </c>
@@ -1409,15 +1653,15 @@
         <v>0.24353505992947111</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
       <c r="C24" s="2">
         <v>260805</v>
       </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
       <c r="G24" s="3">
         <v>0.40005200000000002</v>
       </c>
@@ -1434,23 +1678,23 @@
         <v>0.24551795951722497</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C25" s="1">
         <v>42</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="6" t="s">
         <v>56</v>
       </c>
       <c r="G25" s="3">
@@ -1469,15 +1713,15 @@
         <v>0.13136018668592531</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
       <c r="C26" s="2">
         <v>3407</v>
       </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
       <c r="G26" s="3">
         <v>0.27239600000000003</v>
       </c>
@@ -1494,15 +1738,15 @@
         <v>0.12911306307082634</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
       <c r="C27" s="2">
         <v>260805</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
       <c r="G27" s="3">
         <v>0.27552599999999999</v>
       </c>
@@ -1519,23 +1763,23 @@
         <v>0.13979857366511875</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="6" t="s">
         <v>57</v>
       </c>
       <c r="C28" s="1">
         <v>42</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G28" s="3">
@@ -1554,85 +1798,126 @@
         <v>0.46184643679265741</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="2">
+        <v>3407</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="3">
+        <v>0.54636583807247296</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0.626950246985429</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0.91623270580344196</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0.45816760838325998</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0.43844975941474401</v>
+      </c>
+      <c r="L29" s="5"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="2">
+        <v>260805</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="3">
+        <v>0.54614823839686</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0.62223364816389104</v>
+      </c>
+      <c r="I30" s="3">
+        <v>0.91940912810357001</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0.436426468293235</v>
+      </c>
+      <c r="K30" s="3">
+        <v>0.45754220293764503</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C31" s="1">
         <v>42</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G31" s="3">
         <v>0.55159100000000005</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H31" s="3">
         <v>0.62378199999999995</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I31" s="3">
         <v>0.913103</v>
       </c>
-      <c r="J29" s="3">
+      <c r="J31" s="3">
         <v>0.4510960858929583</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K31" s="3">
         <v>0.4466486544416759</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C32" s="1">
         <v>42</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G32" s="3">
         <v>0.54889900000000003</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H32" s="3">
         <v>0.62326099999999995</v>
       </c>
-      <c r="I30" s="3">
+      <c r="I32" s="3">
         <v>0.91211100000000001</v>
       </c>
-      <c r="J30" s="3">
+      <c r="J32" s="3">
         <v>0.45234006453337466</v>
       </c>
-      <c r="K30" s="3">
+      <c r="K32" s="3">
         <v>0.44677520560964545</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
@@ -1695,10 +1980,12 @@
       <c r="C44" s="1"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
     </row>
@@ -1710,8 +1997,16 @@
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
     </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="38">
     <mergeCell ref="F22:F24"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="B15:B17"/>
@@ -1745,6 +2040,11 @@
     <mergeCell ref="D25:D27"/>
     <mergeCell ref="E25:E27"/>
     <mergeCell ref="F25:F27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="F28:F30"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1753,7 +2053,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A1B1F4-76FC-42C2-BB7C-1F34FCA74F09}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="23.08203125" customWidth="1"/>
@@ -1801,22 +2101,22 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="2">
         <v>42</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>21</v>
       </c>
       <c r="G2" s="3">
@@ -1836,14 +2136,14 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="2">
         <v>3407</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
       <c r="G3" s="3">
         <v>0.49485600000000002</v>
       </c>
@@ -1861,14 +2161,14 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="2">
         <v>260805</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
       <c r="G4" s="3">
         <v>0.501224</v>
       </c>
@@ -1886,19 +2186,19 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C5" s="2">
         <v>42</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G5" s="3">
@@ -1918,13 +2218,13 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="2">
         <v>3407</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
       <c r="G6" s="3">
         <v>0.38905099999999998</v>
       </c>
@@ -1942,13 +2242,13 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="2">
         <v>260805</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
       <c r="G7" s="3">
         <v>0.400341</v>
       </c>
@@ -1966,22 +2266,22 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="6" t="s">
         <v>57</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G8" s="3">
@@ -2001,409 +2301,477 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="2">
+        <v>3407</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="3">
+        <v>0.54636583807247296</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.626950246985429</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.91623270580344196</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.45816760838325998</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0.43844975941474401</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="2">
+        <v>260805</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="3">
+        <v>0.54614823839686</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.62223364816389104</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.91940912810357001</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.436426468293235</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0.45754220293764503</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C11" s="2">
         <v>42</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G11" s="3">
         <v>0.510467</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H11" s="3">
         <v>0.584368</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I11" s="3">
         <v>0.89673400000000003</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J11" s="3">
         <v>0.39396607692965052</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K11" s="3">
         <v>0.4020205635653869</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="2">
         <v>3407</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="3">
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="3">
         <v>0.50480100000000006</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H12" s="3">
         <v>0.58288099999999998</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I12" s="3">
         <v>0.88726499999999997</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J12" s="3">
         <v>0.38876874061434191</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K12" s="3">
         <v>0.401767049156244</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="2">
         <v>260805</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="3">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="3">
         <v>0.505552</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H13" s="3">
         <v>0.59609199999999996</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I13" s="3">
         <v>0.88400800000000002</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J13" s="3">
         <v>0.37774777210855015</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K13" s="3">
         <v>0.40358289345327658</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C14" s="2">
         <v>42</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G14" s="3">
         <v>0.52212000000000003</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H14" s="3">
         <v>0.58928700000000001</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I14" s="3">
         <v>0.91895800000000005</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J14" s="3">
         <v>0.4418979117972538</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K14" s="3">
         <v>0.40833091651871312</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="2">
         <v>3407</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="3">
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="3">
         <v>0.51979500000000001</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H15" s="3">
         <v>0.59313800000000005</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I15" s="3">
         <v>0.90631099999999998</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J15" s="3">
         <v>0.43145114163684051</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K15" s="3">
         <v>0.4020821922741154</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="2">
         <v>260805</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="3">
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="3">
         <v>0.52418100000000001</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H16" s="3">
         <v>0.60394700000000001</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I16" s="3">
         <v>0.90991900000000003</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J16" s="3">
         <v>0.43112222573563386</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K16" s="3">
         <v>0.41892476048844135</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C17" s="2">
         <v>42</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F17" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G17" s="3">
         <v>0.55070300000000005</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H17" s="3">
         <v>0.62163900000000005</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I17" s="3">
         <v>0.92617799999999995</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J17" s="3">
         <v>0.43360562510859202</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K17" s="3">
         <v>0.43913465551816211</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="2">
         <v>3407</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="3">
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="3">
         <v>0.55664999999999998</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H18" s="3">
         <v>0.65718799999999999</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I18" s="3">
         <v>0.92103000000000002</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J18" s="3">
         <v>0.41979254957124068</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K18" s="3">
         <v>0.46905165530976944</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="2">
         <v>260805</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="3">
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="3">
         <v>0.54842800000000003</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H19" s="3">
         <v>0.61980800000000003</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I19" s="3">
         <v>0.91514099999999998</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J19" s="3">
         <v>0.42061203377085771</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K19" s="3">
         <v>0.45019471097050745</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C20" s="2">
         <v>42</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D20" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E20" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F20" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G20" s="3">
         <v>0.55398499999999995</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H20" s="3">
         <v>0.61966500000000002</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I20" s="3">
         <v>0.92775099999999999</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J20" s="3">
         <v>0.44392883384931803</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K20" s="3">
         <v>0.44927937715751454</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="2">
         <v>3407</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="3">
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="3">
         <v>0.54928999999999994</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H21" s="3">
         <v>0.61820299999999995</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I21" s="3">
         <v>0.92330199999999996</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J21" s="3">
         <v>0.44111480901135758</v>
       </c>
-      <c r="K19" s="3">
+      <c r="K21" s="3">
         <v>0.43758028316129016</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="2">
         <v>260805</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="3">
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="3">
         <v>0.54596699999999998</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H22" s="3">
         <v>0.61835600000000002</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I22" s="3">
         <v>0.92196199999999995</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J22" s="3">
         <v>0.4410397863802909</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K22" s="3">
         <v>0.44395605957934431</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-    </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="A23" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="2">
+        <v>42</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="F23" s="4"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
+      <c r="G23" s="3">
+        <v>0.56818310558396101</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0.63233149006921896</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0.93267861619898995</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.463472663987746</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0.45495608256471698</v>
+      </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="2">
+        <v>3407</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
       <c r="F24" s="4"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
+      <c r="G24" s="3">
+        <v>0.56617616308687801</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0.63563997437275299</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0.92756872471941898</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0.45824505718544101</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0.45768990470874399</v>
+      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="2">
+        <v>260805</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
       <c r="F25" s="4"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
+      <c r="G25" s="3">
+        <v>0.57710102869948798</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0.65824756137388496</v>
+      </c>
+      <c r="I25" s="3">
+        <v>0.92979646153705098</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0.45907812238350598</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0.49994136890991803</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
@@ -2562,6 +2930,12 @@
       <c r="K37" s="3"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -2569,46 +2943,3103 @@
       <c r="K38" s="3"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
     </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="F9:F11"/>
+  <mergeCells count="38">
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="D8:D10"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="E5:E7"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="F20:F22"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="B11:B13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86EEE050-6857-442D-A415-5B212CE49A79}">
+  <dimension ref="A1:L48"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="21.9140625" customWidth="1"/>
+    <col min="5" max="5" width="55.58203125" customWidth="1"/>
+    <col min="6" max="6" width="42.4140625" customWidth="1"/>
+    <col min="7" max="7" width="10.4140625" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" customWidth="1"/>
+    <col min="9" max="9" width="16.08203125" customWidth="1"/>
+    <col min="10" max="10" width="22.08203125" customWidth="1"/>
+    <col min="11" max="11" width="22.75" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="2">
+        <v>42</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.52212000000000003</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.58928700000000001</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0.91895800000000005</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.4418979117972538</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0.40833091651871312</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="2">
+        <v>3407</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="3">
+        <v>0.51979500000000001</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.59313800000000005</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.90631099999999998</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.43145114163684051</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0.4020821922741154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2">
+        <v>260805</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="3">
+        <v>0.52418100000000001</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.60394700000000001</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.90991900000000003</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.43112222573563386</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0.41892476048844135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="2">
+        <v>42</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.55398499999999995</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.61966500000000002</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.92775099999999999</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.44392883384931803</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0.44927937715751454</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="2">
+        <v>3407</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="3">
+        <v>0.54928999999999994</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.61820299999999995</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.92330199999999996</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.44111480901135758</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0.43758028316129016</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="2">
+        <v>260805</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="3">
+        <v>0.54596699999999998</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.61835600000000002</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.92196199999999995</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.4410397863802909</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0.44395605957934431</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="2">
+        <v>42</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.52212004508888199</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.58928788738348703</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.91895833617164302</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.44189791179725302</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0.40833091651871301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="2">
+        <v>42</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.52896854779856295</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.59947291930212898</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.90695332370686299</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.44001080173673102</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0.41622701207570501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="2">
+        <v>42</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.53968903628383902</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.60758848011367805</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.91786411781201804</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.44126519847903001</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0.440109528427785</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="2">
+        <v>3407</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="3">
+        <v>0.52912338915431401</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.606445655172413</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.90844311918230103</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.43772513347789899</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0.425137744152424</v>
+      </c>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="2">
+        <v>260805</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="3">
+        <v>0.52942778966960002</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.61307069020622695</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.90548805842643398</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.42297363026100998</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0.42852507121512601</v>
+      </c>
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="2">
+        <v>42</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.53236640207501496</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.60394455086453802</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.91174546506815601</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.43397314383139102</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.43548183173853899</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="2">
+        <v>3407</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="3">
+        <v>0.52601995816869795</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.59540787662153105</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0.91390790431200397</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.44085238758867301</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0.42083420065984001</v>
+      </c>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="2">
+        <v>260805</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="3">
+        <v>0.52677659342643002</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.61238355788483201</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0.89547180188271802</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0.41493735534537302</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0.42438726824532802</v>
+      </c>
+      <c r="L15" s="6"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="2">
+        <v>42</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.52569711753061199</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.602368210758501</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0.91000242227134498</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.40166376812826599</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0.42339581398343601</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="2">
+        <v>42</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.57365292995618</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.65384997378853305</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.929603961302229</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.45667619857358699</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0.48915734250487503</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="2">
+        <v>3407</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="3">
+        <v>0.559724537527306</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.63041686000949104</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0.926951837605961</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.44403316918253</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0.46487840669883401</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="2">
+        <v>260805</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+    </row>
+    <row r="33" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+    </row>
+    <row r="34" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+    </row>
+    <row r="35" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+    </row>
+    <row r="36" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+    </row>
+    <row r="37" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+    </row>
+    <row r="38" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+    </row>
+    <row r="39" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+    </row>
+    <row r="40" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+    </row>
+    <row r="41" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+    </row>
+    <row r="42" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+    </row>
+    <row r="43" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+    </row>
+    <row r="44" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+    </row>
+    <row r="45" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+    </row>
+    <row r="46" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+    </row>
+    <row r="47" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+    </row>
+    <row r="48" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="L13:L15"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="L10:L12"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CC9359-5F4C-43D4-B8C3-BA821FBD1013}">
+  <dimension ref="A1:L156"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="17.83203125" customWidth="1"/>
+    <col min="5" max="5" width="56.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.08203125" customWidth="1"/>
+    <col min="8" max="8" width="11.25" customWidth="1"/>
+    <col min="9" max="9" width="16.08203125" customWidth="1"/>
+    <col min="10" max="10" width="21" customWidth="1"/>
+    <col min="11" max="11" width="19.08203125" customWidth="1"/>
+    <col min="12" max="12" width="12.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="2">
+        <v>42</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.52212000000000003</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.58928700000000001</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0.91895800000000005</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.4418979117972538</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0.40833091651871312</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="2">
+        <v>3407</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="3">
+        <v>0.51979500000000001</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.59313800000000005</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.90631099999999998</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.43145114163684051</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0.4020821922741154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2">
+        <v>260805</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="3">
+        <v>0.52418100000000001</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.60394700000000001</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.90991900000000003</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.43112222573563386</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0.41892476048844135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="2">
+        <v>42</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.52212004508888199</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.58928788738348703</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.91895833617164302</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.44189791179725302</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0.40833091651871301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="2">
+        <v>42</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="3">
+        <v>0.53303060403871205</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.59890550623045602</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.91570727796908402</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.44112559134424301</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0.41248056320834298</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="2">
+        <v>3407</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="3">
+        <v>0.52093389962377701</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.59388350454796501</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.91785094585371496</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.44408068980620402</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0.40471810028658101</v>
+      </c>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="2">
+        <v>260805</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="3">
+        <v>0.52539780717213003</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.60263249207036496</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.90403590276886603</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.42396026962937799</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0.427467645888918</v>
+      </c>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="2">
+        <v>42</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.52951368695243795</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.59477994863309702</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.90816425319320904</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.433619006543633</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0.428653186095172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="2">
+        <v>3407</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="3">
+        <v>0.51571951565304297</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.59197700283801902</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.90266458299264796</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.42852090730305797</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0.40269413470725701</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="2">
+        <v>260805</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="3">
+        <v>0.51577542251419595</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.60150433419822902</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.89329144959073303</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.41721208058554898</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0.40415132086604</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="2">
+        <v>42</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="2">
+        <v>42</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="4"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="4"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="4"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="4"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="4"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="4"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="4"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="4"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="4"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="4"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="4"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="4"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="4"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="4"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="4"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="4"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="4"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="4"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="4"/>
+      <c r="B105" s="4"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="4"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="4"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="4"/>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="4"/>
+      <c r="B110" s="4"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="4"/>
+      <c r="B111" s="4"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="4"/>
+      <c r="B112" s="4"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="4"/>
+      <c r="B113" s="4"/>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="4"/>
+      <c r="B114" s="4"/>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="4"/>
+      <c r="B115" s="4"/>
+      <c r="C115" s="4"/>
+      <c r="D115" s="4"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="4"/>
+      <c r="B116" s="4"/>
+      <c r="C116" s="4"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="4"/>
+      <c r="B117" s="4"/>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="4"/>
+      <c r="B118" s="4"/>
+      <c r="C118" s="4"/>
+      <c r="D118" s="4"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="4"/>
+      <c r="B119" s="4"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="4"/>
+      <c r="B120" s="4"/>
+      <c r="C120" s="4"/>
+      <c r="D120" s="4"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="4"/>
+      <c r="B121" s="4"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="4"/>
+      <c r="B122" s="4"/>
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="4"/>
+      <c r="B123" s="4"/>
+      <c r="C123" s="4"/>
+      <c r="D123" s="4"/>
+      <c r="E123" s="4"/>
+      <c r="F123" s="4"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="4"/>
+      <c r="B124" s="4"/>
+      <c r="C124" s="4"/>
+      <c r="D124" s="4"/>
+      <c r="E124" s="4"/>
+      <c r="F124" s="4"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="4"/>
+      <c r="B125" s="4"/>
+      <c r="C125" s="4"/>
+      <c r="D125" s="4"/>
+      <c r="E125" s="4"/>
+      <c r="F125" s="4"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="4"/>
+      <c r="B126" s="4"/>
+      <c r="C126" s="4"/>
+      <c r="D126" s="4"/>
+      <c r="E126" s="4"/>
+      <c r="F126" s="4"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="4"/>
+      <c r="B127" s="4"/>
+      <c r="C127" s="4"/>
+      <c r="D127" s="4"/>
+      <c r="E127" s="4"/>
+      <c r="F127" s="4"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="4"/>
+      <c r="B128" s="4"/>
+      <c r="C128" s="4"/>
+      <c r="D128" s="4"/>
+      <c r="E128" s="4"/>
+      <c r="F128" s="4"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="4"/>
+      <c r="B129" s="4"/>
+      <c r="C129" s="4"/>
+      <c r="D129" s="4"/>
+      <c r="E129" s="4"/>
+      <c r="F129" s="4"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="4"/>
+      <c r="B130" s="4"/>
+      <c r="C130" s="4"/>
+      <c r="D130" s="4"/>
+      <c r="E130" s="4"/>
+      <c r="F130" s="4"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="4"/>
+      <c r="B131" s="4"/>
+      <c r="C131" s="4"/>
+      <c r="D131" s="4"/>
+      <c r="E131" s="4"/>
+      <c r="F131" s="4"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="4"/>
+      <c r="B132" s="4"/>
+      <c r="C132" s="4"/>
+      <c r="D132" s="4"/>
+      <c r="E132" s="4"/>
+      <c r="F132" s="4"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="4"/>
+      <c r="B133" s="4"/>
+      <c r="C133" s="4"/>
+      <c r="D133" s="4"/>
+      <c r="E133" s="4"/>
+      <c r="F133" s="4"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="4"/>
+      <c r="B134" s="4"/>
+      <c r="C134" s="4"/>
+      <c r="D134" s="4"/>
+      <c r="E134" s="4"/>
+      <c r="F134" s="4"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="4"/>
+      <c r="B135" s="4"/>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="4"/>
+      <c r="B136" s="4"/>
+      <c r="C136" s="4"/>
+      <c r="D136" s="4"/>
+      <c r="E136" s="4"/>
+      <c r="F136" s="4"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="4"/>
+      <c r="B137" s="4"/>
+      <c r="C137" s="4"/>
+      <c r="D137" s="4"/>
+      <c r="E137" s="4"/>
+      <c r="F137" s="4"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="4"/>
+      <c r="B138" s="4"/>
+      <c r="C138" s="4"/>
+      <c r="D138" s="4"/>
+      <c r="E138" s="4"/>
+      <c r="F138" s="4"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="4"/>
+      <c r="B139" s="4"/>
+      <c r="C139" s="4"/>
+      <c r="D139" s="4"/>
+      <c r="E139" s="4"/>
+      <c r="F139" s="4"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="4"/>
+      <c r="B140" s="4"/>
+      <c r="C140" s="4"/>
+      <c r="D140" s="4"/>
+      <c r="E140" s="4"/>
+      <c r="F140" s="4"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="4"/>
+      <c r="B141" s="4"/>
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="4"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="4"/>
+      <c r="B142" s="4"/>
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="4"/>
+      <c r="B143" s="4"/>
+      <c r="C143" s="4"/>
+      <c r="D143" s="4"/>
+      <c r="E143" s="4"/>
+      <c r="F143" s="4"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="4"/>
+      <c r="B144" s="4"/>
+      <c r="C144" s="4"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="4"/>
+      <c r="F144" s="4"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="4"/>
+      <c r="B145" s="4"/>
+      <c r="C145" s="4"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="4"/>
+      <c r="F145" s="4"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="4"/>
+      <c r="B146" s="4"/>
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="4"/>
+      <c r="F146" s="4"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="4"/>
+      <c r="B147" s="4"/>
+      <c r="C147" s="4"/>
+      <c r="D147" s="4"/>
+      <c r="E147" s="4"/>
+      <c r="F147" s="4"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="4"/>
+      <c r="B148" s="4"/>
+      <c r="C148" s="4"/>
+      <c r="D148" s="4"/>
+      <c r="E148" s="4"/>
+      <c r="F148" s="4"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="4"/>
+      <c r="B149" s="4"/>
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="4"/>
+      <c r="B150" s="4"/>
+      <c r="C150" s="4"/>
+      <c r="D150" s="4"/>
+      <c r="E150" s="4"/>
+      <c r="F150" s="4"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="4"/>
+      <c r="B151" s="4"/>
+      <c r="C151" s="4"/>
+      <c r="D151" s="4"/>
+      <c r="E151" s="4"/>
+      <c r="F151" s="4"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="4"/>
+      <c r="B152" s="4"/>
+      <c r="C152" s="4"/>
+      <c r="D152" s="4"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="4"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="4"/>
+      <c r="B153" s="4"/>
+      <c r="C153" s="4"/>
+      <c r="D153" s="4"/>
+      <c r="E153" s="4"/>
+      <c r="F153" s="4"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="4"/>
+      <c r="B154" s="4"/>
+      <c r="C154" s="4"/>
+      <c r="D154" s="4"/>
+      <c r="E154" s="4"/>
+      <c r="F154" s="4"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="4"/>
+      <c r="B155" s="4"/>
+      <c r="C155" s="4"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="4"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="4"/>
+      <c r="B156" s="4"/>
+      <c r="C156" s="4"/>
+      <c r="D156" s="4"/>
+      <c r="E156" s="4"/>
+      <c r="F156" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="F9:F11"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFA399BF-89A0-41EF-AB28-1F8353B1A682}">
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="5" max="5" width="97.33203125" customWidth="1"/>
+    <col min="6" max="6" width="48.5" customWidth="1"/>
+    <col min="8" max="8" width="11.9140625" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" customWidth="1"/>
+    <col min="10" max="10" width="22.25" customWidth="1"/>
+    <col min="11" max="11" width="22.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="2">
+        <v>42</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.57365292995618</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.65384997378853305</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0.929603961302229</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.45667619857358699</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0.48915734250487503</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="2">
+        <v>42</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="3">
+        <v>0.56309315508008395</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.63790240443975499</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.92813609831214905</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.44878354395757603</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0.46571208927401903</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2">
+        <v>3407</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3">
+        <v>0.559724537527306</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.63041686000949104</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.926951837605961</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.44403316918253</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0.46487840669883401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="2">
+        <v>260805</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="3">
+        <v>0.558422676620286</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.63487858233237904</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.92584507303996499</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.44521166999595702</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0.46751667403229502</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="2">
+        <v>42</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3">
+        <v>0.516090983155024</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.59220529017396795</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.90946737559885205</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.41697609466848501</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0.40721926535727798</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="2">
+        <v>42</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="3">
+        <v>0.52369653086081702</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.58777616577283098</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.92425223947715796</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.44622739787513699</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0.37740098033360098</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="2">
+        <v>42</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="3">
+        <v>0.52273482475756405</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.58503587350299802</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.92348047636288899</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.42368422844961001</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0.395691253288114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>